--- a/output/pdf_financials_xlsx/ODX.H.xlsx
+++ b/output/pdf_financials_xlsx/ODX.H.xlsx
@@ -1222,10 +1222,10 @@
         <v>0.707623</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>0.058553</v>
+        <v>-0.058553</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>0.27055</v>
+        <v>-0.27055</v>
       </c>
     </row>
     <row r="17">
@@ -1490,10 +1490,10 @@
         <v>0.707623</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>0.058553</v>
+        <v>-0.058553</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.27055</v>
+        <v>-0.27055</v>
       </c>
     </row>
     <row r="21">
@@ -1646,10 +1646,10 @@
         <v>0.707623</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>0.058553</v>
+        <v>-0.058553</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>0.27055</v>
+        <v>-0.27055</v>
       </c>
     </row>
     <row r="24">
@@ -1884,10 +1884,10 @@
         <v>0.707623</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>0.058553</v>
+        <v>-0.058553</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>0.27055</v>
+        <v>-0.27055</v>
       </c>
     </row>
     <row r="28">
@@ -1988,10 +1988,10 @@
         <v>0.707623</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>0.058553</v>
+        <v>-0.058553</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.27055</v>
+        <v>-0.27055</v>
       </c>
     </row>
     <row r="30">
@@ -2122,10 +2122,10 @@
         <v>0</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -22642,10 +22642,10 @@
         </is>
       </c>
       <c r="R168" s="5" t="n">
-        <v>0.058553</v>
+        <v>-0.058553</v>
       </c>
       <c r="S168" s="5" t="n">
-        <v>0.27055</v>
+        <v>-0.27055</v>
       </c>
     </row>
     <row r="169">

--- a/output/pdf_financials_xlsx/ODX.H.xlsx
+++ b/output/pdf_financials_xlsx/ODX.H.xlsx
@@ -2224,49 +2224,49 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>4.260982</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.851665</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.474903</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.121842</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.85734</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.254083</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.043352</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.044442</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.017388</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.012095</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.013614</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.055188</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.07474699999999999</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.0008</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.018387</v>
       </c>
     </row>
     <row r="35">
@@ -2328,49 +2328,49 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.144873</v>
+        <v>4.405855</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.221376</v>
+        <v>2.073041</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.057074</v>
+        <v>1.531977</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.059662</v>
+        <v>1.181504</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.035049</v>
+        <v>0.892389</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.034944</v>
+        <v>0.289027</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.020973</v>
+        <v>0.06432499999999999</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.018251</v>
+        <v>0.062693</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.017388</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.012095</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.013614</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.055188</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.07474699999999999</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.0008</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.018387</v>
       </c>
     </row>
     <row r="37">
@@ -2952,31 +2952,31 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>4.341683</v>
+        <v>0.08070099999999999</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.7097</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.421789</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.074236</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.832167</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.493272</v>
+        <v>0.239189</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.327646</v>
+        <v>0.284294</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.354067</v>
+        <v>0.309625</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.368201</v>
+        <v>0.350813</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>0</v>
@@ -7867,7 +7867,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -8770,7 +8770,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -13843,7 +13843,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E70" s="5" t="n">
@@ -32396,7 +32396,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">

--- a/output/pdf_financials_xlsx/ODX.H.xlsx
+++ b/output/pdf_financials_xlsx/ODX.H.xlsx
@@ -6163,7 +6163,7 @@
         <v>0</v>
       </c>
       <c r="P107" s="3" t="n">
-        <v>0</v>
+        <v>0.20202</v>
       </c>
     </row>
     <row r="108">
@@ -6555,7 +6555,7 @@
         <v>0</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>0.043518</v>
       </c>
       <c r="I115" s="3" t="n">
         <v>0</v>
@@ -15511,7 +15511,11 @@
           <t>Share-based compensation expense (Note 6)</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
           <t>-</t>
@@ -19153,7 +19157,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
           <t>-</t>
